--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2841" uniqueCount="686">
   <si>
     <t>Processo</t>
   </si>
@@ -1117,22 +1117,34 @@
     <t>2025-07-05</t>
   </si>
   <si>
-    <t>Alessandro Cappi</t>
-  </si>
-  <si>
-    <t>André Caramello</t>
-  </si>
-  <si>
-    <t>Andrey Andrade</t>
-  </si>
-  <si>
-    <t>Mateus Machado</t>
-  </si>
-  <si>
-    <t>André Camargo</t>
-  </si>
-  <si>
-    <t>Leonardo Carmo</t>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>ROSANA.MARTINS</t>
+  </si>
+  <si>
+    <t>JULIANO</t>
+  </si>
+  <si>
+    <t>RAFAELA.MEIRELLES</t>
+  </si>
+  <si>
+    <t>ROSILENE</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
   </si>
   <si>
     <t>SSO</t>
@@ -1156,13 +1168,19 @@
     <t>Equipamento Amostragem</t>
   </si>
   <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>Sonda Multiparâmetros</t>
+  </si>
+  <si>
     <t>Sistema Remediação</t>
   </si>
   <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>Sonda Multiparâmetros</t>
+    <t>Medidor de Vazão Fixo</t>
   </si>
   <si>
     <t>Falco</t>
@@ -1177,22 +1195,34 @@
     <t>ISCO</t>
   </si>
   <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>E3 Point</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>YSI</t>
+  </si>
+  <si>
+    <t>Panther</t>
+  </si>
+  <si>
+    <t>Innova</t>
+  </si>
+  <si>
     <t>QED</t>
   </si>
   <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
-    <t>EXO</t>
+    <t>IQ PLUS</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
   </si>
   <si>
     <t>Thermo</t>
-  </si>
-  <si>
-    <t>YSI</t>
-  </si>
-  <si>
-    <t>Innova</t>
   </si>
   <si>
     <t>Produto</t>
@@ -2486,47 +2516,44 @@
       <c r="F2">
         <v>10000</v>
       </c>
-      <c r="G2" t="s">
-        <v>367</v>
-      </c>
       <c r="J2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O2" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P2" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q2" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R2" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="T2" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="U2" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V2" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -2548,47 +2575,44 @@
       <c r="F3">
         <v>15000</v>
       </c>
-      <c r="G3" t="s">
-        <v>367</v>
-      </c>
       <c r="J3" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L3" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P3" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R3" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S3" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="T3" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="U3" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V3" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -2610,47 +2634,44 @@
       <c r="F4">
         <v>20000</v>
       </c>
-      <c r="G4" t="s">
-        <v>367</v>
-      </c>
       <c r="J4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L4" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M4" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N4" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O4" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P4" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q4" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R4" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S4" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="T4" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="U4" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V4" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -2672,47 +2693,44 @@
       <c r="F5">
         <v>25000</v>
       </c>
-      <c r="G5" t="s">
-        <v>367</v>
-      </c>
       <c r="J5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M5" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N5" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O5" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P5" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q5" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R5" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S5" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="T5" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="U5" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V5" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -2734,47 +2752,44 @@
       <c r="F6">
         <v>12000</v>
       </c>
-      <c r="G6" t="s">
-        <v>368</v>
-      </c>
       <c r="J6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L6" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="M6" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N6" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O6" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P6" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q6" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R6" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S6" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="T6" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="U6" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V6" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2796,47 +2811,44 @@
       <c r="F7">
         <v>18000</v>
       </c>
-      <c r="G7" t="s">
-        <v>367</v>
-      </c>
       <c r="J7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L7" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M7" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N7" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O7" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P7" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q7" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R7" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S7" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="T7" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="U7" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V7" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2858,47 +2870,44 @@
       <c r="F8">
         <v>12000</v>
       </c>
-      <c r="G8" t="s">
-        <v>368</v>
-      </c>
       <c r="J8" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K8" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L8" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="M8" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N8" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O8" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P8" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q8" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R8" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S8" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="T8" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="U8" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V8" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2920,47 +2929,44 @@
       <c r="F9">
         <v>30000</v>
       </c>
-      <c r="G9" t="s">
-        <v>367</v>
-      </c>
       <c r="J9" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L9" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="M9" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N9" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O9" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P9" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q9" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R9" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S9" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="T9" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="U9" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V9" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2982,47 +2988,44 @@
       <c r="F10">
         <v>50000</v>
       </c>
-      <c r="G10" t="s">
-        <v>367</v>
-      </c>
       <c r="J10" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L10" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M10" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N10" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O10" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P10" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q10" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R10" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S10" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="T10" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="U10" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V10" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -3038,47 +3041,44 @@
       <c r="F11">
         <v>8000</v>
       </c>
-      <c r="G11" t="s">
-        <v>367</v>
-      </c>
       <c r="J11" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K11" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L11" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M11" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N11" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O11" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P11" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q11" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R11" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S11" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="T11" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="U11" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V11" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -3100,47 +3100,44 @@
       <c r="F12">
         <v>20000</v>
       </c>
-      <c r="G12" t="s">
-        <v>367</v>
-      </c>
       <c r="J12" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K12" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L12" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M12" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N12" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O12" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P12" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q12" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R12" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S12" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="T12" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="U12" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V12" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -3162,47 +3159,44 @@
       <c r="F13">
         <v>15000</v>
       </c>
-      <c r="G13" t="s">
-        <v>367</v>
-      </c>
       <c r="J13" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L13" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M13" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N13" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O13" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P13" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q13" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R13" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S13" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="T13" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="U13" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V13" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -3224,47 +3218,44 @@
       <c r="F14">
         <v>15000</v>
       </c>
-      <c r="G14" t="s">
-        <v>367</v>
-      </c>
       <c r="J14" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K14" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L14" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M14" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N14" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O14" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P14" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q14" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R14" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S14" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="T14" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="U14" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V14" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -3286,47 +3277,44 @@
       <c r="F15">
         <v>15000</v>
       </c>
-      <c r="G15" t="s">
-        <v>367</v>
-      </c>
       <c r="J15" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K15" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L15" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M15" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N15" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O15" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P15" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q15" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R15" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S15" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="T15" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="U15" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V15" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -3348,47 +3336,44 @@
       <c r="F16">
         <v>15000</v>
       </c>
-      <c r="G16" t="s">
-        <v>367</v>
-      </c>
       <c r="J16" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K16" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L16" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M16" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N16" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O16" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P16" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q16" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R16" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S16" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="T16" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="U16" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V16" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3410,47 +3395,44 @@
       <c r="F17">
         <v>15000</v>
       </c>
-      <c r="G17" t="s">
-        <v>367</v>
-      </c>
       <c r="J17" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K17" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L17" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M17" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N17" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O17" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P17" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q17" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R17" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S17" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="T17" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
       <c r="U17" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V17" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3472,47 +3454,44 @@
       <c r="F18">
         <v>15000</v>
       </c>
-      <c r="G18" t="s">
-        <v>367</v>
-      </c>
       <c r="J18" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K18" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L18" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M18" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N18" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O18" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P18" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q18" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R18" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S18" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="T18" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="U18" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V18" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3534,47 +3513,44 @@
       <c r="F19">
         <v>20000</v>
       </c>
-      <c r="G19" t="s">
-        <v>367</v>
-      </c>
       <c r="J19" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K19" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L19" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M19" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N19" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O19" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P19" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q19" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R19" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S19" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="T19" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="U19" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V19" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3596,47 +3572,44 @@
       <c r="F20">
         <v>20000</v>
       </c>
-      <c r="G20" t="s">
-        <v>367</v>
-      </c>
       <c r="J20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K20" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L20" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M20" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N20" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O20" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P20" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R20" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S20" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="T20" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="U20" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V20" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3658,47 +3631,44 @@
       <c r="F21">
         <v>20000</v>
       </c>
-      <c r="G21" t="s">
-        <v>367</v>
-      </c>
       <c r="J21" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K21" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L21" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M21" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N21" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O21" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P21" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q21" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R21" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S21" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="T21" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="U21" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V21" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -3720,47 +3690,44 @@
       <c r="F22">
         <v>20000</v>
       </c>
-      <c r="G22" t="s">
-        <v>367</v>
-      </c>
       <c r="J22" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K22" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L22" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M22" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N22" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O22" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P22" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q22" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R22" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S22" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="T22" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="U22" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V22" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -3782,47 +3749,44 @@
       <c r="F23">
         <v>20000</v>
       </c>
-      <c r="G23" t="s">
-        <v>367</v>
-      </c>
       <c r="J23" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K23" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L23" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M23" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N23" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O23" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P23" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q23" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R23" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S23" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="T23" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="U23" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V23" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -3844,47 +3808,44 @@
       <c r="F24">
         <v>20000</v>
       </c>
-      <c r="G24" t="s">
-        <v>367</v>
-      </c>
       <c r="J24" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K24" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L24" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M24" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N24" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O24" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P24" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q24" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R24" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S24" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="T24" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="U24" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V24" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -3906,47 +3867,44 @@
       <c r="F25">
         <v>13300</v>
       </c>
-      <c r="G25" t="s">
-        <v>367</v>
-      </c>
       <c r="J25" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K25" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L25" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M25" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N25" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O25" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P25" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q25" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R25" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S25" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="T25" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="U25" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V25" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -3968,47 +3926,44 @@
       <c r="F26">
         <v>13400</v>
       </c>
-      <c r="G26" t="s">
-        <v>367</v>
-      </c>
       <c r="J26" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K26" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L26" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M26" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N26" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O26" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P26" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q26" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R26" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S26" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="T26" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="U26" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V26" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4024,47 +3979,44 @@
       <c r="F27">
         <v>13500</v>
       </c>
-      <c r="G27" t="s">
-        <v>367</v>
-      </c>
       <c r="J27" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K27" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L27" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M27" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N27" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O27" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P27" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q27" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R27" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S27" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="T27" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="U27" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V27" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -4086,47 +4038,44 @@
       <c r="F28">
         <v>13600</v>
       </c>
-      <c r="G28" t="s">
-        <v>367</v>
-      </c>
       <c r="J28" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K28" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L28" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M28" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N28" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O28" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P28" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q28" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R28" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S28" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="T28" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="U28" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V28" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -4148,47 +4097,44 @@
       <c r="F29">
         <v>13700</v>
       </c>
-      <c r="G29" t="s">
-        <v>367</v>
-      </c>
       <c r="J29" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K29" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L29" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M29" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N29" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O29" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P29" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q29" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R29" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S29" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="T29" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="U29" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V29" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -4204,47 +4150,44 @@
       <c r="F30">
         <v>13800</v>
       </c>
-      <c r="G30" t="s">
-        <v>367</v>
-      </c>
       <c r="J30" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K30" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L30" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M30" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N30" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O30" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P30" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q30" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R30" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S30" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="T30" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="U30" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V30" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -4266,47 +4209,44 @@
       <c r="F31">
         <v>13900</v>
       </c>
-      <c r="G31" t="s">
-        <v>367</v>
-      </c>
       <c r="J31" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K31" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L31" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M31" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N31" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O31" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P31" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q31" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R31" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S31" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="T31" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="U31" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V31" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -4328,47 +4268,44 @@
       <c r="F32">
         <v>14000</v>
       </c>
-      <c r="G32" t="s">
-        <v>367</v>
-      </c>
       <c r="J32" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K32" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L32" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M32" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N32" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O32" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P32" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q32" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R32" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S32" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="T32" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="U32" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V32" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -4384,47 +4321,44 @@
       <c r="F33">
         <v>14100</v>
       </c>
-      <c r="G33" t="s">
-        <v>367</v>
-      </c>
       <c r="J33" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K33" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L33" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M33" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N33" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O33" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P33" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q33" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R33" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S33" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="T33" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="U33" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V33" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -4446,47 +4380,44 @@
       <c r="F34">
         <v>14200</v>
       </c>
-      <c r="G34" t="s">
-        <v>367</v>
-      </c>
       <c r="J34" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K34" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L34" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M34" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N34" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O34" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P34" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q34" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R34" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S34" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="T34" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="U34" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V34" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -4508,47 +4439,44 @@
       <c r="F35">
         <v>14300</v>
       </c>
-      <c r="G35" t="s">
-        <v>367</v>
-      </c>
       <c r="J35" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K35" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L35" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M35" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N35" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O35" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P35" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q35" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R35" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S35" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="T35" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="U35" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V35" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="36" spans="1:22">
@@ -4564,47 +4492,44 @@
       <c r="F36">
         <v>14400</v>
       </c>
-      <c r="G36" t="s">
-        <v>367</v>
-      </c>
       <c r="J36" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K36" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L36" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M36" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N36" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O36" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P36" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q36" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R36" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S36" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="T36" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="U36" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V36" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -4626,47 +4551,44 @@
       <c r="F37">
         <v>14500</v>
       </c>
-      <c r="G37" t="s">
-        <v>367</v>
-      </c>
       <c r="J37" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K37" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L37" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M37" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N37" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O37" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P37" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q37" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R37" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S37" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="T37" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="U37" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V37" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -4688,47 +4610,44 @@
       <c r="F38">
         <v>14600</v>
       </c>
-      <c r="G38" t="s">
-        <v>367</v>
-      </c>
       <c r="J38" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K38" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L38" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M38" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N38" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O38" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P38" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q38" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R38" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S38" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="T38" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="U38" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V38" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -4744,47 +4663,44 @@
       <c r="F39">
         <v>14700</v>
       </c>
-      <c r="G39" t="s">
-        <v>367</v>
-      </c>
       <c r="J39" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K39" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L39" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M39" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N39" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O39" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P39" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q39" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R39" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S39" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="T39" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="U39" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V39" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="40" spans="1:22">
@@ -4806,47 +4722,44 @@
       <c r="F40">
         <v>14800</v>
       </c>
-      <c r="G40" t="s">
-        <v>367</v>
-      </c>
       <c r="J40" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K40" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L40" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M40" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N40" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O40" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P40" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q40" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R40" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S40" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="T40" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="U40" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V40" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="41" spans="1:22">
@@ -4868,47 +4781,44 @@
       <c r="F41">
         <v>14900</v>
       </c>
-      <c r="G41" t="s">
-        <v>367</v>
-      </c>
       <c r="J41" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K41" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L41" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M41" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N41" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O41" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P41" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q41" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R41" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S41" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="T41" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="U41" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V41" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -4924,47 +4834,44 @@
       <c r="F42">
         <v>15000</v>
       </c>
-      <c r="G42" t="s">
-        <v>367</v>
-      </c>
       <c r="J42" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K42" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L42" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M42" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N42" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O42" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P42" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q42" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R42" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S42" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="T42" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="U42" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V42" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -4986,47 +4893,44 @@
       <c r="F43">
         <v>15100</v>
       </c>
-      <c r="G43" t="s">
-        <v>367</v>
-      </c>
       <c r="J43" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K43" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L43" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M43" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N43" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O43" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P43" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q43" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R43" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S43" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="T43" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="U43" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V43" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="44" spans="1:22">
@@ -5048,47 +4952,44 @@
       <c r="F44">
         <v>15200</v>
       </c>
-      <c r="G44" t="s">
-        <v>367</v>
-      </c>
       <c r="J44" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K44" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L44" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M44" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N44" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O44" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P44" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q44" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R44" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S44" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="T44" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="U44" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V44" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="45" spans="1:22">
@@ -5104,47 +5005,44 @@
       <c r="F45">
         <v>15300</v>
       </c>
-      <c r="G45" t="s">
-        <v>367</v>
-      </c>
       <c r="J45" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K45" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L45" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M45" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N45" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O45" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P45" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q45" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R45" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S45" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="T45" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="U45" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V45" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="46" spans="1:22">
@@ -5166,47 +5064,44 @@
       <c r="F46">
         <v>15400</v>
       </c>
-      <c r="G46" t="s">
-        <v>367</v>
-      </c>
       <c r="J46" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K46" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L46" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N46" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O46" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P46" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q46" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R46" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S46" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="T46" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="U46" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V46" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="47" spans="1:22">
@@ -5228,47 +5123,44 @@
       <c r="F47">
         <v>15500</v>
       </c>
-      <c r="G47" t="s">
-        <v>367</v>
-      </c>
       <c r="J47" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K47" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L47" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N47" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O47" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P47" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q47" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R47" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S47" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="T47" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="U47" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V47" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="48" spans="1:22">
@@ -5284,47 +5176,44 @@
       <c r="F48">
         <v>15600</v>
       </c>
-      <c r="G48" t="s">
-        <v>367</v>
-      </c>
       <c r="J48" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K48" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N48" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O48" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q48" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R48" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S48" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="T48" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="U48" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V48" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="49" spans="1:22">
@@ -5346,47 +5235,44 @@
       <c r="F49">
         <v>15700</v>
       </c>
-      <c r="G49" t="s">
-        <v>367</v>
-      </c>
       <c r="J49" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K49" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L49" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N49" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O49" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P49" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q49" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R49" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S49" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="T49" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="U49" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V49" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="50" spans="1:22">
@@ -5408,47 +5294,44 @@
       <c r="F50">
         <v>15800</v>
       </c>
-      <c r="G50" t="s">
-        <v>367</v>
-      </c>
       <c r="J50" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K50" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L50" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N50" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O50" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P50" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q50" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R50" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S50" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="T50" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="U50" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V50" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="51" spans="1:22">
@@ -5464,47 +5347,44 @@
       <c r="F51">
         <v>15900</v>
       </c>
-      <c r="G51" t="s">
-        <v>367</v>
-      </c>
       <c r="J51" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K51" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L51" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M51" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N51" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O51" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P51" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q51" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R51" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S51" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="T51" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="U51" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V51" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="52" spans="1:22">
@@ -5526,47 +5406,44 @@
       <c r="F52">
         <v>16000</v>
       </c>
-      <c r="G52" t="s">
-        <v>367</v>
-      </c>
       <c r="J52" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K52" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M52" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N52" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O52" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P52" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q52" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R52" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S52" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="T52" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="U52" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V52" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="53" spans="1:22">
@@ -5588,47 +5465,44 @@
       <c r="F53">
         <v>16100</v>
       </c>
-      <c r="G53" t="s">
-        <v>367</v>
-      </c>
       <c r="J53" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K53" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L53" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N53" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O53" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P53" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q53" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R53" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S53" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="T53" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="U53" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V53" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="54" spans="1:22">
@@ -5644,47 +5518,44 @@
       <c r="F54">
         <v>16200</v>
       </c>
-      <c r="G54" t="s">
-        <v>367</v>
-      </c>
       <c r="J54" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K54" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N54" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O54" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P54" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q54" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R54" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S54" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="T54" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="U54" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V54" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="55" spans="1:22">
@@ -5706,47 +5577,44 @@
       <c r="F55">
         <v>16300</v>
       </c>
-      <c r="G55" t="s">
-        <v>367</v>
-      </c>
       <c r="J55" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K55" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L55" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O55" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P55" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q55" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R55" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S55" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="T55" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
       <c r="U55" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V55" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="56" spans="1:22">
@@ -5768,47 +5636,44 @@
       <c r="F56">
         <v>16400</v>
       </c>
-      <c r="G56" t="s">
-        <v>367</v>
-      </c>
       <c r="J56" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K56" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L56" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M56" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N56" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O56" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P56" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q56" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R56" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S56" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="T56" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
       <c r="U56" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V56" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="57" spans="1:22">
@@ -5824,47 +5689,44 @@
       <c r="F57">
         <v>16500</v>
       </c>
-      <c r="G57" t="s">
-        <v>367</v>
-      </c>
       <c r="J57" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K57" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L57" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M57" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N57" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O57" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P57" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q57" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R57" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S57" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="T57" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="U57" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V57" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="58" spans="1:22">
@@ -5886,47 +5748,44 @@
       <c r="F58">
         <v>16600</v>
       </c>
-      <c r="G58" t="s">
-        <v>367</v>
-      </c>
       <c r="J58" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K58" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L58" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M58" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N58" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O58" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P58" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q58" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R58" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S58" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="T58" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="U58" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V58" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="59" spans="1:22">
@@ -5948,47 +5807,44 @@
       <c r="F59">
         <v>16700</v>
       </c>
-      <c r="G59" t="s">
-        <v>367</v>
-      </c>
       <c r="J59" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K59" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N59" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O59" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P59" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q59" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R59" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S59" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="T59" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="U59" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V59" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -6004,47 +5860,44 @@
       <c r="F60">
         <v>16800</v>
       </c>
-      <c r="G60" t="s">
-        <v>367</v>
-      </c>
       <c r="J60" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K60" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L60" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N60" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O60" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P60" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q60" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R60" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S60" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="T60" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="U60" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V60" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="61" spans="1:22">
@@ -6066,47 +5919,44 @@
       <c r="F61">
         <v>16900</v>
       </c>
-      <c r="G61" t="s">
-        <v>367</v>
-      </c>
       <c r="J61" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K61" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L61" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M61" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N61" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O61" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P61" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q61" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R61" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S61" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="T61" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="U61" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V61" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="62" spans="1:22">
@@ -6128,47 +5978,44 @@
       <c r="F62">
         <v>17000</v>
       </c>
-      <c r="G62" t="s">
-        <v>367</v>
-      </c>
       <c r="J62" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K62" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L62" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M62" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N62" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O62" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P62" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q62" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R62" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S62" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="T62" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="U62" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V62" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="63" spans="1:22">
@@ -6191,46 +6038,49 @@
         <v>50000</v>
       </c>
       <c r="G63" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H63" t="s">
+        <v>374</v>
       </c>
       <c r="J63" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K63" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L63" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M63" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N63" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O63" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P63" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q63" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R63" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S63" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="T63" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="U63" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V63" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="64" spans="1:22">
@@ -6253,49 +6103,49 @@
         <v>30000</v>
       </c>
       <c r="G64" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H64" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J64" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K64" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L64" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M64" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N64" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O64" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P64" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q64" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R64" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S64" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="T64" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="U64" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V64" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="65" spans="1:22">
@@ -6318,46 +6168,46 @@
         <v>20000</v>
       </c>
       <c r="H65" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J65" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K65" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="L65" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="M65" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N65" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O65" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P65" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q65" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R65" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S65" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="T65" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="U65" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V65" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="66" spans="1:22">
@@ -6380,46 +6230,46 @@
         <v>15000</v>
       </c>
       <c r="G66" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J66" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K66" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L66" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M66" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N66" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O66" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P66" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q66" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R66" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S66" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="T66" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="U66" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V66" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="67" spans="1:22">
@@ -6442,49 +6292,49 @@
         <v>25000</v>
       </c>
       <c r="G67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H67" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J67" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K67" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L67" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="M67" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N67" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O67" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P67" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q67" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R67" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S67" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="T67" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="U67" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V67" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="68" spans="1:22">
@@ -6507,46 +6357,49 @@
         <v>20000</v>
       </c>
       <c r="G68" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H68" t="s">
+        <v>374</v>
       </c>
       <c r="J68" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K68" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M68" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N68" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O68" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P68" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q68" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R68" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S68" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="T68" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="U68" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V68" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="69" spans="1:22">
@@ -6569,46 +6422,49 @@
         <v>20000</v>
       </c>
       <c r="G69" t="s">
-        <v>370</v>
+        <v>367</v>
+      </c>
+      <c r="H69" t="s">
+        <v>374</v>
       </c>
       <c r="J69" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K69" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L69" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="M69" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N69" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O69" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P69" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q69" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R69" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S69" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="T69" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="U69" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V69" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="70" spans="1:22">
@@ -6631,46 +6487,46 @@
         <v>35000</v>
       </c>
       <c r="H70" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J70" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K70" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="L70" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N70" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O70" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P70" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q70" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R70" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S70" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="T70" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="U70" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V70" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="71" spans="1:22">
@@ -6693,49 +6549,49 @@
         <v>45000</v>
       </c>
       <c r="G71" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H71" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J71" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K71" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L71" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="M71" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N71" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O71" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P71" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q71" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R71" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S71" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="T71" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="U71" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V71" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="72" spans="1:22">
@@ -6758,46 +6614,49 @@
         <v>28000</v>
       </c>
       <c r="G72" t="s">
-        <v>370</v>
+        <v>367</v>
+      </c>
+      <c r="H72" t="s">
+        <v>375</v>
       </c>
       <c r="J72" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K72" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="L72" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="M72" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N72" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O72" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P72" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q72" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R72" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S72" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="T72" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="U72" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V72" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="73" spans="1:22">
@@ -6820,49 +6679,49 @@
         <v>32000</v>
       </c>
       <c r="G73" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H73" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J73" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K73" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L73" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="M73" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N73" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O73" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P73" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q73" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R73" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S73" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="T73" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="U73" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V73" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="74" spans="1:22">
@@ -6884,47 +6743,44 @@
       <c r="F74">
         <v>15500</v>
       </c>
-      <c r="G74" t="s">
-        <v>369</v>
-      </c>
       <c r="J74" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K74" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L74" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M74" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N74" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O74" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P74" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q74" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R74" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S74" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="T74" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="U74" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V74" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="75" spans="1:22">
@@ -6949,44 +6805,47 @@
       <c r="G75" t="s">
         <v>369</v>
       </c>
+      <c r="H75" t="s">
+        <v>374</v>
+      </c>
       <c r="J75" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K75" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L75" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M75" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N75" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O75" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P75" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q75" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R75" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S75" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="T75" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="U75" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V75" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="76" spans="1:22">
@@ -7008,47 +6867,47 @@
       <c r="F76">
         <v>16500</v>
       </c>
-      <c r="G76" t="s">
-        <v>369</v>
+      <c r="H76" t="s">
+        <v>375</v>
       </c>
       <c r="J76" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K76" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L76" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M76" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N76" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O76" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P76" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q76" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R76" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S76" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="T76" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="U76" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V76" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="77" spans="1:22">
@@ -7071,46 +6930,49 @@
         <v>17000</v>
       </c>
       <c r="G77" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+      <c r="H77" t="s">
+        <v>375</v>
       </c>
       <c r="J77" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K77" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L77" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M77" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N77" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O77" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P77" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q77" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R77" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S77" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="T77" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="U77" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V77" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="78" spans="1:22">
@@ -7132,47 +6994,44 @@
       <c r="F78">
         <v>17500</v>
       </c>
-      <c r="G78" t="s">
-        <v>369</v>
-      </c>
       <c r="J78" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K78" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L78" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M78" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N78" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O78" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P78" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q78" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R78" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S78" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="T78" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="U78" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V78" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="79" spans="1:22">
@@ -7195,46 +7054,49 @@
         <v>18000</v>
       </c>
       <c r="G79" t="s">
-        <v>369</v>
+        <v>368</v>
+      </c>
+      <c r="H79" t="s">
+        <v>375</v>
       </c>
       <c r="J79" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K79" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L79" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M79" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N79" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O79" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P79" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q79" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R79" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S79" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="T79" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="U79" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V79" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="80" spans="1:22">
@@ -7256,47 +7118,47 @@
       <c r="F80">
         <v>18500</v>
       </c>
-      <c r="G80" t="s">
-        <v>369</v>
+      <c r="H80" t="s">
+        <v>376</v>
       </c>
       <c r="J80" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K80" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L80" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M80" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N80" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O80" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P80" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q80" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R80" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S80" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="T80" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="U80" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V80" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="81" spans="1:22">
@@ -7319,46 +7181,49 @@
         <v>19000</v>
       </c>
       <c r="G81" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H81" t="s">
+        <v>374</v>
       </c>
       <c r="J81" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K81" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L81" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M81" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N81" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O81" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P81" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q81" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R81" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S81" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="T81" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="U81" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V81" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="82" spans="1:22">
@@ -7380,47 +7245,44 @@
       <c r="F82">
         <v>19500</v>
       </c>
-      <c r="G82" t="s">
-        <v>369</v>
-      </c>
       <c r="J82" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K82" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L82" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M82" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N82" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O82" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P82" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q82" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R82" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S82" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="T82" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="U82" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V82" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="83" spans="1:22">
@@ -7443,46 +7305,49 @@
         <v>20000</v>
       </c>
       <c r="G83" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H83" t="s">
+        <v>374</v>
       </c>
       <c r="J83" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K83" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L83" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M83" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N83" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O83" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P83" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q83" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R83" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S83" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="T83" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="U83" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V83" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="84" spans="1:22">
@@ -7504,47 +7369,47 @@
       <c r="F84">
         <v>20500</v>
       </c>
-      <c r="G84" t="s">
-        <v>369</v>
+      <c r="H84" t="s">
+        <v>376</v>
       </c>
       <c r="J84" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K84" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L84" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M84" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N84" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O84" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P84" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q84" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R84" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S84" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="T84" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="U84" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V84" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="85" spans="1:22">
@@ -7569,44 +7434,47 @@
       <c r="G85" t="s">
         <v>369</v>
       </c>
+      <c r="H85" t="s">
+        <v>375</v>
+      </c>
       <c r="J85" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K85" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L85" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M85" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N85" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O85" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P85" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q85" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R85" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S85" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="T85" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="U85" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V85" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="86" spans="1:22">
@@ -7628,47 +7496,44 @@
       <c r="F86">
         <v>21500</v>
       </c>
-      <c r="G86" t="s">
-        <v>369</v>
-      </c>
       <c r="J86" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K86" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L86" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M86" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N86" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O86" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P86" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q86" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R86" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S86" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="T86" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="U86" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V86" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="87" spans="1:22">
@@ -7691,46 +7556,49 @@
         <v>22000</v>
       </c>
       <c r="G87" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+      <c r="H87" t="s">
+        <v>374</v>
       </c>
       <c r="J87" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K87" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L87" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M87" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N87" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O87" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P87" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q87" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R87" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S87" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="T87" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="U87" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V87" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="88" spans="1:22">
@@ -7752,47 +7620,47 @@
       <c r="F88">
         <v>22500</v>
       </c>
-      <c r="G88" t="s">
-        <v>369</v>
+      <c r="H88" t="s">
+        <v>375</v>
       </c>
       <c r="J88" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K88" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L88" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M88" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N88" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O88" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P88" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q88" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R88" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S88" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="T88" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="U88" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V88" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="89" spans="1:22">
@@ -7815,46 +7683,49 @@
         <v>23000</v>
       </c>
       <c r="G89" t="s">
-        <v>369</v>
+        <v>368</v>
+      </c>
+      <c r="H89" t="s">
+        <v>375</v>
       </c>
       <c r="J89" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K89" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L89" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M89" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N89" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O89" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P89" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q89" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R89" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S89" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="T89" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="U89" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V89" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="90" spans="1:22">
@@ -7876,47 +7747,44 @@
       <c r="F90">
         <v>23500</v>
       </c>
-      <c r="G90" t="s">
-        <v>369</v>
-      </c>
       <c r="J90" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K90" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L90" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M90" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N90" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O90" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P90" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q90" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R90" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S90" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="T90" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="U90" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V90" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="91" spans="1:22">
@@ -7939,46 +7807,49 @@
         <v>24000</v>
       </c>
       <c r="G91" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H91" t="s">
+        <v>375</v>
       </c>
       <c r="J91" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K91" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L91" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M91" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N91" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O91" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P91" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q91" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R91" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S91" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="T91" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="U91" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V91" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="92" spans="1:22">
@@ -8000,47 +7871,47 @@
       <c r="F92">
         <v>24500</v>
       </c>
-      <c r="G92" t="s">
-        <v>369</v>
+      <c r="H92" t="s">
+        <v>376</v>
       </c>
       <c r="J92" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K92" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L92" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M92" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N92" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O92" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P92" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q92" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R92" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S92" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="T92" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="U92" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V92" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="93" spans="1:22">
@@ -8063,46 +7934,49 @@
         <v>25000</v>
       </c>
       <c r="G93" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H93" t="s">
+        <v>374</v>
       </c>
       <c r="J93" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K93" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L93" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M93" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N93" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O93" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P93" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q93" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R93" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S93" t="s">
-        <v>491</v>
+        <v>501</v>
       </c>
       <c r="T93" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="U93" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V93" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="94" spans="1:22">
@@ -8124,47 +7998,44 @@
       <c r="F94">
         <v>25500</v>
       </c>
-      <c r="G94" t="s">
-        <v>369</v>
-      </c>
       <c r="J94" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K94" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L94" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M94" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N94" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O94" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P94" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q94" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R94" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S94" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="T94" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="U94" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V94" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="95" spans="1:22">
@@ -8189,44 +8060,47 @@
       <c r="G95" t="s">
         <v>369</v>
       </c>
+      <c r="H95" t="s">
+        <v>374</v>
+      </c>
       <c r="J95" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K95" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L95" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M95" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N95" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O95" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P95" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q95" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R95" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S95" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="T95" t="s">
-        <v>628</v>
+        <v>638</v>
       </c>
       <c r="U95" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V95" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="96" spans="1:22">
@@ -8248,47 +8122,47 @@
       <c r="F96">
         <v>26500</v>
       </c>
-      <c r="G96" t="s">
-        <v>369</v>
+      <c r="H96" t="s">
+        <v>376</v>
       </c>
       <c r="J96" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K96" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L96" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M96" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N96" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O96" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P96" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q96" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R96" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S96" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="T96" t="s">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="U96" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V96" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="97" spans="1:22">
@@ -8311,46 +8185,49 @@
         <v>27000</v>
       </c>
       <c r="G97" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+      <c r="H97" t="s">
+        <v>375</v>
       </c>
       <c r="J97" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K97" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L97" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M97" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N97" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O97" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P97" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q97" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R97" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S97" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="T97" t="s">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="U97" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V97" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="98" spans="1:22">
@@ -8372,47 +8249,44 @@
       <c r="F98">
         <v>27500</v>
       </c>
-      <c r="G98" t="s">
-        <v>369</v>
-      </c>
       <c r="J98" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K98" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L98" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M98" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N98" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O98" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P98" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q98" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R98" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S98" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="T98" t="s">
-        <v>631</v>
+        <v>641</v>
       </c>
       <c r="U98" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V98" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="99" spans="1:22">
@@ -8435,46 +8309,49 @@
         <v>28000</v>
       </c>
       <c r="G99" t="s">
-        <v>369</v>
+        <v>368</v>
+      </c>
+      <c r="H99" t="s">
+        <v>374</v>
       </c>
       <c r="J99" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K99" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L99" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M99" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N99" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O99" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P99" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q99" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R99" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S99" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="T99" t="s">
-        <v>632</v>
+        <v>642</v>
       </c>
       <c r="U99" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V99" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="100" spans="1:22">
@@ -8496,47 +8373,47 @@
       <c r="F100">
         <v>28500</v>
       </c>
-      <c r="G100" t="s">
-        <v>369</v>
+      <c r="H100" t="s">
+        <v>375</v>
       </c>
       <c r="J100" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K100" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L100" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M100" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N100" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O100" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P100" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q100" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R100" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S100" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="T100" t="s">
-        <v>633</v>
+        <v>643</v>
       </c>
       <c r="U100" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V100" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:22">
@@ -8559,46 +8436,49 @@
         <v>29000</v>
       </c>
       <c r="G101" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H101" t="s">
+        <v>375</v>
       </c>
       <c r="J101" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K101" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L101" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M101" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N101" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O101" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P101" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q101" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R101" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S101" t="s">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="T101" t="s">
-        <v>634</v>
+        <v>644</v>
       </c>
       <c r="U101" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V101" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="102" spans="1:22">
@@ -8620,47 +8500,44 @@
       <c r="F102">
         <v>29500</v>
       </c>
-      <c r="G102" t="s">
-        <v>369</v>
-      </c>
       <c r="J102" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K102" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L102" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M102" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N102" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O102" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P102" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q102" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R102" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S102" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="T102" t="s">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="U102" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V102" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="103" spans="1:22">
@@ -8683,46 +8560,49 @@
         <v>30000</v>
       </c>
       <c r="G103" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H103" t="s">
+        <v>375</v>
       </c>
       <c r="J103" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K103" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L103" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M103" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N103" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O103" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P103" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q103" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R103" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S103" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="T103" t="s">
-        <v>636</v>
+        <v>646</v>
       </c>
       <c r="U103" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V103" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="104" spans="1:22">
@@ -8744,47 +8624,47 @@
       <c r="F104">
         <v>30500</v>
       </c>
-      <c r="G104" t="s">
-        <v>369</v>
+      <c r="H104" t="s">
+        <v>376</v>
       </c>
       <c r="J104" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K104" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L104" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M104" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N104" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O104" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P104" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q104" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R104" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S104" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="T104" t="s">
-        <v>637</v>
+        <v>647</v>
       </c>
       <c r="U104" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V104" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="105" spans="1:22">
@@ -8809,44 +8689,47 @@
       <c r="G105" t="s">
         <v>369</v>
       </c>
+      <c r="H105" t="s">
+        <v>374</v>
+      </c>
       <c r="J105" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K105" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L105" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M105" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N105" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O105" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P105" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q105" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R105" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S105" t="s">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="T105" t="s">
-        <v>638</v>
+        <v>648</v>
       </c>
       <c r="U105" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V105" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="106" spans="1:22">
@@ -8868,47 +8751,44 @@
       <c r="F106">
         <v>31500</v>
       </c>
-      <c r="G106" t="s">
-        <v>369</v>
-      </c>
       <c r="J106" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K106" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L106" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M106" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N106" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O106" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P106" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q106" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R106" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S106" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="T106" t="s">
-        <v>639</v>
+        <v>649</v>
       </c>
       <c r="U106" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V106" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="107" spans="1:22">
@@ -8931,46 +8811,49 @@
         <v>32000</v>
       </c>
       <c r="G107" t="s">
-        <v>369</v>
+        <v>371</v>
+      </c>
+      <c r="H107" t="s">
+        <v>374</v>
       </c>
       <c r="J107" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K107" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L107" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M107" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N107" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O107" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P107" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q107" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R107" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S107" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="T107" t="s">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="U107" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V107" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="108" spans="1:22">
@@ -8992,47 +8875,47 @@
       <c r="F108">
         <v>32500</v>
       </c>
-      <c r="G108" t="s">
-        <v>369</v>
+      <c r="H108" t="s">
+        <v>376</v>
       </c>
       <c r="J108" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K108" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="L108" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="M108" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N108" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O108" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P108" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q108" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R108" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S108" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="T108" t="s">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="U108" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V108" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="109" spans="1:22">
@@ -9055,46 +8938,49 @@
         <v>33000</v>
       </c>
       <c r="G109" t="s">
-        <v>369</v>
+        <v>368</v>
+      </c>
+      <c r="H109" t="s">
+        <v>375</v>
       </c>
       <c r="J109" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K109" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L109" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="M109" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N109" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O109" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P109" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q109" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R109" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S109" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="T109" t="s">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="U109" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V109" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="110" spans="1:22">
@@ -9116,47 +9002,44 @@
       <c r="F110">
         <v>33500</v>
       </c>
-      <c r="G110" t="s">
-        <v>369</v>
-      </c>
       <c r="J110" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K110" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L110" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M110" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="N110" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O110" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P110" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q110" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R110" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S110" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
       <c r="T110" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="U110" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V110" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="111" spans="1:22">
@@ -9179,46 +9062,49 @@
         <v>34000</v>
       </c>
       <c r="G111" t="s">
-        <v>369</v>
+        <v>370</v>
+      </c>
+      <c r="H111" t="s">
+        <v>374</v>
       </c>
       <c r="J111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K111" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L111" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M111" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N111" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O111" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P111" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q111" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R111" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S111" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="T111" t="s">
-        <v>644</v>
+        <v>654</v>
       </c>
       <c r="U111" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V111" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="112" spans="1:22">
@@ -9240,47 +9126,47 @@
       <c r="F112">
         <v>34500</v>
       </c>
-      <c r="G112" t="s">
-        <v>369</v>
+      <c r="H112" t="s">
+        <v>375</v>
       </c>
       <c r="J112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K112" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L112" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M112" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="N112" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O112" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P112" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q112" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R112" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S112" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="T112" t="s">
-        <v>645</v>
+        <v>655</v>
       </c>
       <c r="U112" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V112" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="113" spans="1:22">
@@ -9303,46 +9189,49 @@
         <v>35000</v>
       </c>
       <c r="G113" t="s">
-        <v>369</v>
+        <v>367</v>
+      </c>
+      <c r="H113" t="s">
+        <v>375</v>
       </c>
       <c r="J113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K113" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="L113" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M113" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="N113" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O113" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P113" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q113" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R113" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S113" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="T113" t="s">
-        <v>646</v>
+        <v>656</v>
       </c>
       <c r="U113" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V113" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="114" spans="1:22">
@@ -9364,50 +9253,47 @@
       <c r="F114">
         <v>10000</v>
       </c>
-      <c r="G114" t="s">
-        <v>369</v>
-      </c>
-      <c r="I114" t="s">
-        <v>371</v>
+      <c r="H114" t="s">
+        <v>374</v>
       </c>
       <c r="J114" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L114" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M114" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N114" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O114" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P114" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q114" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R114" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S114" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="T114" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="U114" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V114" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="115" spans="1:22">
@@ -9429,50 +9315,47 @@
       <c r="F115">
         <v>8000</v>
       </c>
-      <c r="G115" t="s">
-        <v>369</v>
-      </c>
       <c r="I115" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J115" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K115" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L115" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M115" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N115" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O115" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P115" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q115" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R115" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S115" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="T115" t="s">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="U115" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V115" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="116" spans="1:22">
@@ -9494,50 +9377,47 @@
       <c r="F116">
         <v>12000</v>
       </c>
-      <c r="G116" t="s">
-        <v>370</v>
-      </c>
-      <c r="I116" t="s">
-        <v>372</v>
+      <c r="H116" t="s">
+        <v>375</v>
       </c>
       <c r="J116" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K116" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="L116" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="M116" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N116" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O116" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P116" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q116" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R116" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S116" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="T116" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="U116" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V116" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="117" spans="1:22">
@@ -9559,50 +9439,47 @@
       <c r="F117">
         <v>10000</v>
       </c>
-      <c r="G117" t="s">
-        <v>370</v>
-      </c>
       <c r="I117" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="J117" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K117" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="L117" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="M117" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N117" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O117" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P117" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q117" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R117" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S117" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="T117" t="s">
-        <v>648</v>
+        <v>658</v>
       </c>
       <c r="U117" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V117" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="118" spans="1:22">
@@ -9624,50 +9501,47 @@
       <c r="F118">
         <v>15000</v>
       </c>
-      <c r="G118" t="s">
-        <v>369</v>
-      </c>
-      <c r="I118" t="s">
-        <v>370</v>
+      <c r="H118" t="s">
+        <v>376</v>
       </c>
       <c r="J118" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K118" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="L118" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="M118" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N118" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O118" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P118" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q118" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R118" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S118" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="T118" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="U118" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V118" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="119" spans="1:22">
@@ -9689,50 +9563,47 @@
       <c r="F119">
         <v>5000</v>
       </c>
-      <c r="G119" t="s">
-        <v>369</v>
-      </c>
       <c r="I119" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J119" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K119" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="L119" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="M119" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N119" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O119" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P119" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q119" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R119" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S119" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="T119" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="U119" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V119" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="120" spans="1:22">
@@ -9754,50 +9625,47 @@
       <c r="F120">
         <v>8000</v>
       </c>
-      <c r="G120" t="s">
-        <v>369</v>
-      </c>
       <c r="I120" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="J120" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K120" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L120" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="M120" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N120" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O120" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P120" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q120" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R120" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S120" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="T120" t="s">
-        <v>649</v>
+        <v>659</v>
       </c>
       <c r="U120" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V120" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="121" spans="1:22">
@@ -9811,58 +9679,55 @@
         <v>259</v>
       </c>
       <c r="D121" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="E121" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F121">
-        <v>15000</v>
-      </c>
-      <c r="G121" t="s">
-        <v>370</v>
+        <v>18000</v>
       </c>
       <c r="I121" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J121" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K121" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L121" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M121" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N121" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O121" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P121" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q121" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R121" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S121" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="T121" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="U121" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V121" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="122" spans="1:22">
@@ -9876,58 +9741,55 @@
         <v>259</v>
       </c>
       <c r="D122" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="E122" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="F122">
         <v>12000</v>
       </c>
-      <c r="G122" t="s">
-        <v>370</v>
-      </c>
       <c r="I122" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J122" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K122" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L122" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M122" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N122" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O122" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P122" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q122" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R122" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S122" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="T122" t="s">
-        <v>650</v>
+        <v>660</v>
       </c>
       <c r="U122" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V122" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="123" spans="1:22">
@@ -9941,58 +9803,58 @@
         <v>260</v>
       </c>
       <c r="D123" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E123" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F123">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="G123" t="s">
-        <v>370</v>
-      </c>
-      <c r="I123" t="s">
-        <v>371</v>
+        <v>367</v>
+      </c>
+      <c r="H123" t="s">
+        <v>375</v>
       </c>
       <c r="J123" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K123" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="L123" t="s">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="M123" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N123" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O123" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P123" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q123" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R123" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S123" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="T123" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="U123" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V123" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="124" spans="1:22">
@@ -10006,58 +9868,58 @@
         <v>260</v>
       </c>
       <c r="D124" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="E124" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F124">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="G124" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I124" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J124" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K124" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="L124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M124" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N124" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O124" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P124" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q124" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R124" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S124" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="T124" t="s">
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="U124" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V124" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="125" spans="1:22">
@@ -10071,58 +9933,55 @@
         <v>261</v>
       </c>
       <c r="D125" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E125" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F125">
         <v>15000</v>
       </c>
-      <c r="G125" t="s">
-        <v>370</v>
-      </c>
-      <c r="I125" t="s">
-        <v>371</v>
+      <c r="H125" t="s">
+        <v>374</v>
       </c>
       <c r="J125" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K125" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L125" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M125" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N125" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O125" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P125" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q125" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R125" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S125" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="T125" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="U125" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V125" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="126" spans="1:22">
@@ -10136,58 +9995,55 @@
         <v>261</v>
       </c>
       <c r="D126" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="E126" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="F126">
         <v>12000</v>
       </c>
-      <c r="G126" t="s">
-        <v>370</v>
-      </c>
       <c r="I126" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J126" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K126" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L126" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M126" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N126" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O126" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P126" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q126" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R126" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S126" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="T126" t="s">
-        <v>652</v>
+        <v>662</v>
       </c>
       <c r="U126" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V126" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="127" spans="1:22">
@@ -10201,58 +10057,55 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E127" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="F127">
-        <v>15000</v>
-      </c>
-      <c r="G127" t="s">
-        <v>370</v>
-      </c>
-      <c r="I127" t="s">
-        <v>371</v>
+        <v>14000</v>
+      </c>
+      <c r="H127" t="s">
+        <v>375</v>
       </c>
       <c r="J127" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K127" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L127" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M127" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N127" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O127" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P127" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q127" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R127" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S127" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="T127" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="U127" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V127" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="128" spans="1:22">
@@ -10266,58 +10119,55 @@
         <v>262</v>
       </c>
       <c r="D128" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="E128" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="F128">
-        <v>12000</v>
-      </c>
-      <c r="G128" t="s">
-        <v>370</v>
+        <v>11000</v>
       </c>
       <c r="I128" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J128" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K128" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M128" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N128" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O128" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P128" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q128" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R128" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S128" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="T128" t="s">
-        <v>653</v>
+        <v>663</v>
       </c>
       <c r="U128" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V128" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="129" spans="1:23">
@@ -10331,58 +10181,55 @@
         <v>263</v>
       </c>
       <c r="D129" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E129" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F129">
-        <v>15000</v>
-      </c>
-      <c r="G129" t="s">
-        <v>370</v>
-      </c>
-      <c r="I129" t="s">
-        <v>371</v>
+        <v>16000</v>
+      </c>
+      <c r="H129" t="s">
+        <v>376</v>
       </c>
       <c r="J129" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K129" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="L129" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="M129" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N129" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O129" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P129" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q129" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R129" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S129" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="T129" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="U129" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V129" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="130" spans="1:23">
@@ -10396,58 +10243,55 @@
         <v>263</v>
       </c>
       <c r="D130" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E130" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F130">
-        <v>12000</v>
-      </c>
-      <c r="G130" t="s">
-        <v>370</v>
+        <v>13000</v>
       </c>
       <c r="I130" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J130" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K130" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="L130" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="M130" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N130" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O130" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P130" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q130" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R130" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S130" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="T130" t="s">
-        <v>654</v>
+        <v>664</v>
       </c>
       <c r="U130" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V130" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="131" spans="1:23">
@@ -10461,58 +10305,55 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E131" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F131">
         <v>15000</v>
       </c>
-      <c r="G131" t="s">
-        <v>370</v>
-      </c>
-      <c r="I131" t="s">
-        <v>371</v>
+      <c r="H131" t="s">
+        <v>374</v>
       </c>
       <c r="J131" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K131" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L131" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M131" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N131" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O131" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P131" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q131" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R131" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S131" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="T131" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="U131" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V131" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="132" spans="1:23">
@@ -10526,58 +10367,55 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E132" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="F132">
         <v>12000</v>
       </c>
-      <c r="G132" t="s">
-        <v>370</v>
-      </c>
       <c r="I132" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J132" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K132" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L132" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M132" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N132" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O132" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P132" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q132" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R132" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S132" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="T132" t="s">
-        <v>655</v>
+        <v>665</v>
       </c>
       <c r="U132" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V132" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="133" spans="1:23">
@@ -10591,58 +10429,55 @@
         <v>265</v>
       </c>
       <c r="D133" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E133" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="F133">
-        <v>15000</v>
-      </c>
-      <c r="G133" t="s">
-        <v>370</v>
-      </c>
-      <c r="I133" t="s">
-        <v>371</v>
+        <v>14000</v>
+      </c>
+      <c r="H133" t="s">
+        <v>375</v>
       </c>
       <c r="J133" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K133" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L133" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="M133" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N133" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O133" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P133" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q133" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R133" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S133" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="T133" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="U133" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V133" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="134" spans="1:23">
@@ -10656,58 +10491,55 @@
         <v>265</v>
       </c>
       <c r="D134" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="E134" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="F134">
-        <v>12000</v>
-      </c>
-      <c r="G134" t="s">
-        <v>370</v>
+        <v>11000</v>
       </c>
       <c r="I134" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J134" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K134" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="L134" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M134" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N134" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O134" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P134" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q134" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R134" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S134" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="T134" t="s">
-        <v>656</v>
+        <v>666</v>
       </c>
       <c r="U134" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V134" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
     </row>
     <row r="135" spans="1:23">
@@ -10733,46 +10565,46 @@
         <v>367</v>
       </c>
       <c r="J135" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K135" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L135" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M135" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N135" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O135" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P135" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q135" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R135" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S135" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
       <c r="T135" t="s">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="U135" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V135" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W135" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:23">
@@ -10798,46 +10630,46 @@
         <v>367</v>
       </c>
       <c r="J136" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K136" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L136" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M136" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N136" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O136" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P136" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q136" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R136" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S136" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="T136" t="s">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="U136" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V136" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W136" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:23">
@@ -10863,46 +10695,46 @@
         <v>367</v>
       </c>
       <c r="J137" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K137" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L137" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="M137" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N137" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O137" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P137" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>410</v>
+      </c>
+      <c r="R137" t="s">
+        <v>411</v>
+      </c>
+      <c r="S137" t="s">
+        <v>534</v>
+      </c>
+      <c r="T137" t="s">
+        <v>669</v>
+      </c>
+      <c r="U137" t="s">
+        <v>682</v>
+      </c>
+      <c r="V137" t="s">
+        <v>683</v>
+      </c>
+      <c r="W137" t="s">
         <v>399</v>
-      </c>
-      <c r="Q137" t="s">
-        <v>400</v>
-      </c>
-      <c r="R137" t="s">
-        <v>401</v>
-      </c>
-      <c r="S137" t="s">
-        <v>524</v>
-      </c>
-      <c r="T137" t="s">
-        <v>659</v>
-      </c>
-      <c r="U137" t="s">
-        <v>672</v>
-      </c>
-      <c r="V137" t="s">
-        <v>673</v>
-      </c>
-      <c r="W137" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:23">
@@ -10928,46 +10760,46 @@
         <v>367</v>
       </c>
       <c r="J138" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K138" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L138" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="M138" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N138" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O138" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P138" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q138" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R138" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S138" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="T138" t="s">
-        <v>660</v>
+        <v>670</v>
       </c>
       <c r="U138" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V138" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W138" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:23">
@@ -10993,46 +10825,46 @@
         <v>367</v>
       </c>
       <c r="J139" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K139" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L139" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M139" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N139" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O139" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P139" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q139" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R139" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S139" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="T139" t="s">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="U139" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V139" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W139" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
     </row>
     <row r="140" spans="1:23">
@@ -11058,46 +10890,46 @@
         <v>367</v>
       </c>
       <c r="J140" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K140" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L140" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="M140" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N140" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O140" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P140" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q140" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R140" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S140" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="T140" t="s">
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="U140" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V140" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W140" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
     </row>
     <row r="141" spans="1:23">
@@ -11123,46 +10955,46 @@
         <v>367</v>
       </c>
       <c r="J141" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K141" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L141" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M141" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N141" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O141" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P141" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q141" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R141" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S141" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="T141" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="U141" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V141" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W141" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:23">
@@ -11188,46 +11020,46 @@
         <v>367</v>
       </c>
       <c r="J142" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K142" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L142" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M142" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N142" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O142" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P142" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q142" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R142" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S142" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="T142" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="U142" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V142" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W142" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:23">
@@ -11253,46 +11085,46 @@
         <v>367</v>
       </c>
       <c r="J143" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K143" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L143" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="M143" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N143" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O143" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P143" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>410</v>
+      </c>
+      <c r="R143" t="s">
+        <v>411</v>
+      </c>
+      <c r="S143" t="s">
+        <v>540</v>
+      </c>
+      <c r="T143" t="s">
+        <v>675</v>
+      </c>
+      <c r="U143" t="s">
+        <v>682</v>
+      </c>
+      <c r="V143" t="s">
+        <v>683</v>
+      </c>
+      <c r="W143" t="s">
         <v>399</v>
-      </c>
-      <c r="Q143" t="s">
-        <v>400</v>
-      </c>
-      <c r="R143" t="s">
-        <v>401</v>
-      </c>
-      <c r="S143" t="s">
-        <v>530</v>
-      </c>
-      <c r="T143" t="s">
-        <v>665</v>
-      </c>
-      <c r="U143" t="s">
-        <v>672</v>
-      </c>
-      <c r="V143" t="s">
-        <v>673</v>
-      </c>
-      <c r="W143" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:23">
@@ -11318,46 +11150,46 @@
         <v>367</v>
       </c>
       <c r="J144" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K144" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L144" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="M144" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N144" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O144" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P144" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q144" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R144" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S144" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="T144" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="U144" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V144" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W144" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="145" spans="1:23">
@@ -11383,46 +11215,46 @@
         <v>367</v>
       </c>
       <c r="J145" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K145" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L145" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M145" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N145" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O145" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P145" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q145" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R145" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S145" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="T145" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="U145" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V145" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W145" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
     </row>
     <row r="146" spans="1:23">
@@ -11448,46 +11280,46 @@
         <v>367</v>
       </c>
       <c r="J146" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K146" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L146" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="M146" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N146" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O146" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P146" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q146" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R146" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S146" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="T146" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="U146" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V146" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W146" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
     </row>
     <row r="147" spans="1:23">
@@ -11510,49 +11342,49 @@
         <v>35000</v>
       </c>
       <c r="G147" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J147" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K147" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L147" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M147" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N147" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O147" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P147" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q147" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R147" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S147" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="T147" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="U147" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V147" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W147" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="148" spans="1:23">
@@ -11575,49 +11407,49 @@
         <v>35000</v>
       </c>
       <c r="G148" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J148" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K148" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L148" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="M148" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N148" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O148" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P148" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q148" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R148" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S148" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="T148" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="U148" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V148" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W148" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:23">
@@ -11640,49 +11472,49 @@
         <v>40000</v>
       </c>
       <c r="G149" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J149" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K149" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L149" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="M149" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N149" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O149" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P149" t="s">
+        <v>409</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>410</v>
+      </c>
+      <c r="R149" t="s">
+        <v>411</v>
+      </c>
+      <c r="S149" t="s">
+        <v>545</v>
+      </c>
+      <c r="T149" t="s">
+        <v>680</v>
+      </c>
+      <c r="U149" t="s">
+        <v>682</v>
+      </c>
+      <c r="V149" t="s">
+        <v>683</v>
+      </c>
+      <c r="W149" t="s">
         <v>399</v>
-      </c>
-      <c r="Q149" t="s">
-        <v>400</v>
-      </c>
-      <c r="R149" t="s">
-        <v>401</v>
-      </c>
-      <c r="S149" t="s">
-        <v>535</v>
-      </c>
-      <c r="T149" t="s">
-        <v>670</v>
-      </c>
-      <c r="U149" t="s">
-        <v>672</v>
-      </c>
-      <c r="V149" t="s">
-        <v>673</v>
-      </c>
-      <c r="W149" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="150" spans="1:23">
@@ -11705,49 +11537,49 @@
         <v>40000</v>
       </c>
       <c r="G150" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J150" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K150" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L150" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="M150" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N150" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O150" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P150" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q150" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R150" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S150" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="T150" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="U150" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V150" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W150" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:23">
@@ -11770,49 +11602,49 @@
         <v>37500</v>
       </c>
       <c r="G151" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J151" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K151" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="L151" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M151" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N151" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O151" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P151" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q151" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R151" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S151" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="T151" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="U151" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V151" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W151" t="s">
-        <v>674</v>
+        <v>684</v>
       </c>
     </row>
     <row r="152" spans="1:23">
@@ -11835,49 +11667,49 @@
         <v>37500</v>
       </c>
       <c r="G152" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="J152" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K152" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L152" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="M152" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="N152" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O152" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="P152" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="Q152" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="R152" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="S152" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="T152" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="U152" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="V152" t="s">
-        <v>673</v>
+        <v>683</v>
       </c>
       <c r="W152" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -2520,10 +2520,10 @@
         <v>330</v>
       </c>
       <c r="F2">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="G2">
-        <v>44000</v>
+        <v>8800</v>
       </c>
       <c r="H2" t="s">
         <v>368</v>
@@ -2588,10 +2588,10 @@
         <v>331</v>
       </c>
       <c r="F3">
-        <v>60000</v>
+        <v>12000</v>
       </c>
       <c r="G3">
-        <v>66000</v>
+        <v>13200</v>
       </c>
       <c r="H3" t="s">
         <v>369</v>
@@ -2656,10 +2656,10 @@
         <v>332</v>
       </c>
       <c r="F4">
-        <v>80000</v>
+        <v>15000</v>
       </c>
       <c r="G4">
-        <v>88000</v>
+        <v>16500</v>
       </c>
       <c r="H4" t="s">
         <v>370</v>
@@ -2724,10 +2724,10 @@
         <v>320</v>
       </c>
       <c r="F5">
-        <v>100000</v>
+        <v>18000</v>
       </c>
       <c r="G5">
-        <v>110000</v>
+        <v>19800</v>
       </c>
       <c r="H5" t="s">
         <v>368</v>
@@ -2792,10 +2792,10 @@
         <v>333</v>
       </c>
       <c r="F6">
-        <v>48000</v>
+        <v>10000</v>
       </c>
       <c r="G6">
-        <v>52800.00000000001</v>
+        <v>11000</v>
       </c>
       <c r="H6" t="s">
         <v>369</v>
@@ -2860,10 +2860,10 @@
         <v>328</v>
       </c>
       <c r="F7">
-        <v>72000</v>
+        <v>13000</v>
       </c>
       <c r="G7">
-        <v>79200</v>
+        <v>14300</v>
       </c>
       <c r="H7" t="s">
         <v>370</v>
@@ -2928,10 +2928,10 @@
         <v>328</v>
       </c>
       <c r="F8">
-        <v>48000</v>
+        <v>9000</v>
       </c>
       <c r="G8">
-        <v>52800.00000000001</v>
+        <v>9900</v>
       </c>
       <c r="H8" t="s">
         <v>370</v>
@@ -2996,10 +2996,10 @@
         <v>310</v>
       </c>
       <c r="F9">
-        <v>120000</v>
+        <v>105000</v>
       </c>
       <c r="G9">
-        <v>132000</v>
+        <v>115500</v>
       </c>
       <c r="H9" t="s">
         <v>368</v>
@@ -3064,10 +3064,10 @@
         <v>334</v>
       </c>
       <c r="F10">
-        <v>150000</v>
+        <v>16000</v>
       </c>
       <c r="G10">
-        <v>165000</v>
+        <v>17600</v>
       </c>
       <c r="H10" t="s">
         <v>369</v>
@@ -3126,10 +3126,10 @@
         <v>335</v>
       </c>
       <c r="F11">
-        <v>32000</v>
+        <v>6000</v>
       </c>
       <c r="G11">
-        <v>35200</v>
+        <v>6600.000000000001</v>
       </c>
       <c r="H11" t="s">
         <v>370</v>
@@ -3194,10 +3194,10 @@
         <v>312</v>
       </c>
       <c r="F12">
-        <v>80000</v>
+        <v>14000</v>
       </c>
       <c r="G12">
-        <v>88000</v>
+        <v>15400</v>
       </c>
       <c r="H12" t="s">
         <v>368</v>
@@ -3262,10 +3262,10 @@
         <v>336</v>
       </c>
       <c r="F13">
-        <v>65000</v>
+        <v>14000</v>
       </c>
       <c r="G13">
-        <v>71500</v>
+        <v>15400</v>
       </c>
       <c r="H13" t="s">
         <v>369</v>
@@ -3330,10 +3330,10 @@
         <v>335</v>
       </c>
       <c r="F14">
-        <v>70000</v>
+        <v>16000</v>
       </c>
       <c r="G14">
-        <v>77000</v>
+        <v>17600</v>
       </c>
       <c r="H14" t="s">
         <v>370</v>
@@ -3398,10 +3398,10 @@
         <v>337</v>
       </c>
       <c r="F15">
-        <v>75000</v>
+        <v>18000</v>
       </c>
       <c r="G15">
-        <v>82500</v>
+        <v>19800</v>
       </c>
       <c r="H15" t="s">
         <v>368</v>
@@ -3466,10 +3466,10 @@
         <v>319</v>
       </c>
       <c r="F16">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="G16">
-        <v>88000</v>
+        <v>22000</v>
       </c>
       <c r="H16" t="s">
         <v>369</v>
@@ -3534,10 +3534,10 @@
         <v>320</v>
       </c>
       <c r="F17">
-        <v>85000</v>
+        <v>22000</v>
       </c>
       <c r="G17">
-        <v>93500.00000000001</v>
+        <v>24200</v>
       </c>
       <c r="H17" t="s">
         <v>370</v>
@@ -3602,10 +3602,10 @@
         <v>321</v>
       </c>
       <c r="F18">
-        <v>90000</v>
+        <v>24000</v>
       </c>
       <c r="G18">
-        <v>99000.00000000001</v>
+        <v>26400</v>
       </c>
       <c r="H18" t="s">
         <v>368</v>
@@ -3670,10 +3670,10 @@
         <v>335</v>
       </c>
       <c r="F19">
-        <v>80000</v>
+        <v>14000</v>
       </c>
       <c r="G19">
-        <v>88000</v>
+        <v>15400</v>
       </c>
       <c r="H19" t="s">
         <v>371</v>
@@ -3738,10 +3738,10 @@
         <v>337</v>
       </c>
       <c r="F20">
-        <v>90000</v>
+        <v>16000</v>
       </c>
       <c r="G20">
-        <v>99000.00000000001</v>
+        <v>17600</v>
       </c>
       <c r="H20" t="s">
         <v>372</v>
@@ -3806,10 +3806,10 @@
         <v>319</v>
       </c>
       <c r="F21">
-        <v>100000</v>
+        <v>18000</v>
       </c>
       <c r="G21">
-        <v>110000</v>
+        <v>19800</v>
       </c>
       <c r="H21" t="s">
         <v>371</v>
@@ -3874,10 +3874,10 @@
         <v>320</v>
       </c>
       <c r="F22">
-        <v>110000</v>
+        <v>20000</v>
       </c>
       <c r="G22">
-        <v>121000</v>
+        <v>22000</v>
       </c>
       <c r="H22" t="s">
         <v>372</v>
@@ -3942,10 +3942,10 @@
         <v>321</v>
       </c>
       <c r="F23">
-        <v>120000</v>
+        <v>22000</v>
       </c>
       <c r="G23">
-        <v>132000</v>
+        <v>24200</v>
       </c>
       <c r="H23" t="s">
         <v>371</v>
@@ -4010,10 +4010,10 @@
         <v>322</v>
       </c>
       <c r="F24">
-        <v>130000</v>
+        <v>105000</v>
       </c>
       <c r="G24">
-        <v>143000</v>
+        <v>115500</v>
       </c>
       <c r="H24" t="s">
         <v>372</v>
@@ -4078,10 +4078,10 @@
         <v>323</v>
       </c>
       <c r="F25">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="G25">
-        <v>41800</v>
+        <v>5500</v>
       </c>
       <c r="H25" t="s">
         <v>369</v>
@@ -4146,10 +4146,10 @@
         <v>324</v>
       </c>
       <c r="F26">
-        <v>39000</v>
+        <v>5300</v>
       </c>
       <c r="G26">
-        <v>42900</v>
+        <v>5830.000000000001</v>
       </c>
       <c r="H26" t="s">
         <v>370</v>
@@ -4208,10 +4208,10 @@
         <v>319</v>
       </c>
       <c r="F27">
-        <v>40000</v>
+        <v>5600</v>
       </c>
       <c r="G27">
-        <v>44000</v>
+        <v>6160.000000000001</v>
       </c>
       <c r="H27" t="s">
         <v>368</v>
@@ -4276,10 +4276,10 @@
         <v>338</v>
       </c>
       <c r="F28">
-        <v>41000</v>
+        <v>5900</v>
       </c>
       <c r="G28">
-        <v>45100.00000000001</v>
+        <v>6490.000000000001</v>
       </c>
       <c r="H28" t="s">
         <v>369</v>
@@ -4344,10 +4344,10 @@
         <v>339</v>
       </c>
       <c r="F29">
-        <v>42000</v>
+        <v>6200</v>
       </c>
       <c r="G29">
-        <v>46200.00000000001</v>
+        <v>6820.000000000001</v>
       </c>
       <c r="H29" t="s">
         <v>370</v>
@@ -4406,10 +4406,10 @@
         <v>322</v>
       </c>
       <c r="F30">
-        <v>43000</v>
+        <v>6500</v>
       </c>
       <c r="G30">
-        <v>47300.00000000001</v>
+        <v>7150.000000000001</v>
       </c>
       <c r="H30" t="s">
         <v>368</v>
@@ -4474,10 +4474,10 @@
         <v>288</v>
       </c>
       <c r="F31">
-        <v>44000</v>
+        <v>6800</v>
       </c>
       <c r="G31">
-        <v>48400.00000000001</v>
+        <v>7480.000000000001</v>
       </c>
       <c r="H31" t="s">
         <v>369</v>
@@ -4542,10 +4542,10 @@
         <v>340</v>
       </c>
       <c r="F32">
-        <v>45000</v>
+        <v>7100</v>
       </c>
       <c r="G32">
-        <v>49500.00000000001</v>
+        <v>7810.000000000001</v>
       </c>
       <c r="H32" t="s">
         <v>370</v>
@@ -4604,10 +4604,10 @@
         <v>341</v>
       </c>
       <c r="F33">
-        <v>46000</v>
+        <v>7400</v>
       </c>
       <c r="G33">
-        <v>50600.00000000001</v>
+        <v>8140.000000000001</v>
       </c>
       <c r="H33" t="s">
         <v>368</v>
@@ -4672,10 +4672,10 @@
         <v>342</v>
       </c>
       <c r="F34">
-        <v>47000</v>
+        <v>7700</v>
       </c>
       <c r="G34">
-        <v>51700.00000000001</v>
+        <v>8470</v>
       </c>
       <c r="H34" t="s">
         <v>369</v>
@@ -4740,10 +4740,10 @@
         <v>343</v>
       </c>
       <c r="F35">
-        <v>48000</v>
+        <v>8000</v>
       </c>
       <c r="G35">
-        <v>52800.00000000001</v>
+        <v>8800</v>
       </c>
       <c r="H35" t="s">
         <v>370</v>
@@ -4802,10 +4802,10 @@
         <v>344</v>
       </c>
       <c r="F36">
-        <v>49000</v>
+        <v>8300</v>
       </c>
       <c r="G36">
-        <v>53900.00000000001</v>
+        <v>9130</v>
       </c>
       <c r="H36" t="s">
         <v>368</v>
@@ -4870,10 +4870,10 @@
         <v>332</v>
       </c>
       <c r="F37">
-        <v>50000</v>
+        <v>8600</v>
       </c>
       <c r="G37">
-        <v>55000.00000000001</v>
+        <v>9460</v>
       </c>
       <c r="H37" t="s">
         <v>369</v>
@@ -4938,10 +4938,10 @@
         <v>336</v>
       </c>
       <c r="F38">
-        <v>51000</v>
+        <v>8900</v>
       </c>
       <c r="G38">
-        <v>56100.00000000001</v>
+        <v>9790</v>
       </c>
       <c r="H38" t="s">
         <v>370</v>
@@ -5000,10 +5000,10 @@
         <v>345</v>
       </c>
       <c r="F39">
-        <v>52000</v>
+        <v>9200</v>
       </c>
       <c r="G39">
-        <v>57200.00000000001</v>
+        <v>10120</v>
       </c>
       <c r="H39" t="s">
         <v>368</v>
@@ -5068,10 +5068,10 @@
         <v>337</v>
       </c>
       <c r="F40">
-        <v>53000</v>
+        <v>9500</v>
       </c>
       <c r="G40">
-        <v>58300.00000000001</v>
+        <v>10450</v>
       </c>
       <c r="H40" t="s">
         <v>369</v>
@@ -5136,10 +5136,10 @@
         <v>319</v>
       </c>
       <c r="F41">
-        <v>54000</v>
+        <v>9800</v>
       </c>
       <c r="G41">
-        <v>59400.00000000001</v>
+        <v>10780</v>
       </c>
       <c r="H41" t="s">
         <v>370</v>
@@ -5198,10 +5198,10 @@
         <v>346</v>
       </c>
       <c r="F42">
-        <v>55000</v>
+        <v>10100</v>
       </c>
       <c r="G42">
-        <v>60500.00000000001</v>
+        <v>11110</v>
       </c>
       <c r="H42" t="s">
         <v>368</v>
@@ -5266,10 +5266,10 @@
         <v>321</v>
       </c>
       <c r="F43">
-        <v>56000</v>
+        <v>10400</v>
       </c>
       <c r="G43">
-        <v>61600.00000000001</v>
+        <v>11440</v>
       </c>
       <c r="H43" t="s">
         <v>369</v>
@@ -5334,10 +5334,10 @@
         <v>322</v>
       </c>
       <c r="F44">
-        <v>57000</v>
+        <v>10700</v>
       </c>
       <c r="G44">
-        <v>62700.00000000001</v>
+        <v>11770</v>
       </c>
       <c r="H44" t="s">
         <v>370</v>
@@ -5396,10 +5396,10 @@
         <v>335</v>
       </c>
       <c r="F45">
-        <v>58000</v>
+        <v>11000</v>
       </c>
       <c r="G45">
-        <v>63800.00000000001</v>
+        <v>12100</v>
       </c>
       <c r="H45" t="s">
         <v>368</v>
@@ -5464,10 +5464,10 @@
         <v>324</v>
       </c>
       <c r="F46">
-        <v>59000</v>
+        <v>11300</v>
       </c>
       <c r="G46">
-        <v>64900.00000000001</v>
+        <v>12430</v>
       </c>
       <c r="H46" t="s">
         <v>369</v>
@@ -5532,10 +5532,10 @@
         <v>328</v>
       </c>
       <c r="F47">
-        <v>60000</v>
+        <v>11600</v>
       </c>
       <c r="G47">
-        <v>66000</v>
+        <v>12760</v>
       </c>
       <c r="H47" t="s">
         <v>370</v>
@@ -5594,10 +5594,10 @@
         <v>320</v>
       </c>
       <c r="F48">
-        <v>61000</v>
+        <v>11900</v>
       </c>
       <c r="G48">
-        <v>67100</v>
+        <v>13090</v>
       </c>
       <c r="H48" t="s">
         <v>368</v>
@@ -5662,10 +5662,10 @@
         <v>339</v>
       </c>
       <c r="F49">
-        <v>62000</v>
+        <v>12200</v>
       </c>
       <c r="G49">
-        <v>68200</v>
+        <v>13420</v>
       </c>
       <c r="H49" t="s">
         <v>369</v>
@@ -5730,10 +5730,10 @@
         <v>329</v>
       </c>
       <c r="F50">
-        <v>63000</v>
+        <v>12500</v>
       </c>
       <c r="G50">
-        <v>69300</v>
+        <v>13750</v>
       </c>
       <c r="H50" t="s">
         <v>370</v>
@@ -5792,10 +5792,10 @@
         <v>323</v>
       </c>
       <c r="F51">
-        <v>64000</v>
+        <v>12800</v>
       </c>
       <c r="G51">
-        <v>70400</v>
+        <v>14080</v>
       </c>
       <c r="H51" t="s">
         <v>368</v>
@@ -5860,10 +5860,10 @@
         <v>340</v>
       </c>
       <c r="F52">
-        <v>65000</v>
+        <v>13100</v>
       </c>
       <c r="G52">
-        <v>71500</v>
+        <v>14410</v>
       </c>
       <c r="H52" t="s">
         <v>369</v>
@@ -5928,10 +5928,10 @@
         <v>345</v>
       </c>
       <c r="F53">
-        <v>66000</v>
+        <v>13400</v>
       </c>
       <c r="G53">
-        <v>72600</v>
+        <v>14740</v>
       </c>
       <c r="H53" t="s">
         <v>370</v>
@@ -5990,10 +5990,10 @@
         <v>347</v>
       </c>
       <c r="F54">
-        <v>67000</v>
+        <v>13700</v>
       </c>
       <c r="G54">
-        <v>73700</v>
+        <v>15070</v>
       </c>
       <c r="H54" t="s">
         <v>368</v>
@@ -6058,10 +6058,10 @@
         <v>343</v>
       </c>
       <c r="F55">
-        <v>68000</v>
+        <v>14000</v>
       </c>
       <c r="G55">
-        <v>74800</v>
+        <v>15400</v>
       </c>
       <c r="H55" t="s">
         <v>369</v>
@@ -6126,10 +6126,10 @@
         <v>346</v>
       </c>
       <c r="F56">
-        <v>69000</v>
+        <v>14300</v>
       </c>
       <c r="G56">
-        <v>75900</v>
+        <v>15730</v>
       </c>
       <c r="H56" t="s">
         <v>370</v>
@@ -6188,10 +6188,10 @@
         <v>330</v>
       </c>
       <c r="F57">
-        <v>70000</v>
+        <v>14600</v>
       </c>
       <c r="G57">
-        <v>77000</v>
+        <v>16060</v>
       </c>
       <c r="H57" t="s">
         <v>368</v>
@@ -6256,10 +6256,10 @@
         <v>336</v>
       </c>
       <c r="F58">
-        <v>71000</v>
+        <v>14900</v>
       </c>
       <c r="G58">
-        <v>78100</v>
+        <v>16390</v>
       </c>
       <c r="H58" t="s">
         <v>369</v>
@@ -6324,10 +6324,10 @@
         <v>335</v>
       </c>
       <c r="F59">
-        <v>72000</v>
+        <v>15200</v>
       </c>
       <c r="G59">
-        <v>79200</v>
+        <v>16720</v>
       </c>
       <c r="H59" t="s">
         <v>370</v>
@@ -6386,10 +6386,10 @@
         <v>342</v>
       </c>
       <c r="F60">
-        <v>73000</v>
+        <v>15500</v>
       </c>
       <c r="G60">
-        <v>80300</v>
+        <v>17050</v>
       </c>
       <c r="H60" t="s">
         <v>368</v>
@@ -6454,10 +6454,10 @@
         <v>319</v>
       </c>
       <c r="F61">
-        <v>74000</v>
+        <v>15800</v>
       </c>
       <c r="G61">
-        <v>81400</v>
+        <v>17380</v>
       </c>
       <c r="H61" t="s">
         <v>369</v>
@@ -6522,10 +6522,10 @@
         <v>320</v>
       </c>
       <c r="F62">
-        <v>75000</v>
+        <v>16100</v>
       </c>
       <c r="G62">
-        <v>82500</v>
+        <v>17710</v>
       </c>
       <c r="H62" t="s">
         <v>370</v>
@@ -7338,10 +7338,10 @@
         <v>351</v>
       </c>
       <c r="F74">
-        <v>20500</v>
+        <v>7400</v>
       </c>
       <c r="G74">
-        <v>22550</v>
+        <v>8140.000000000001</v>
       </c>
       <c r="H74" t="s">
         <v>373</v>
@@ -7406,10 +7406,10 @@
         <v>352</v>
       </c>
       <c r="F75">
-        <v>21000</v>
+        <v>7800</v>
       </c>
       <c r="G75">
-        <v>23100</v>
+        <v>8580</v>
       </c>
       <c r="H75" t="s">
         <v>371</v>
@@ -7474,10 +7474,10 @@
         <v>348</v>
       </c>
       <c r="F76">
-        <v>21500</v>
+        <v>8200</v>
       </c>
       <c r="G76">
-        <v>23650</v>
+        <v>9020</v>
       </c>
       <c r="H76" t="s">
         <v>371</v>
@@ -7542,10 +7542,10 @@
         <v>353</v>
       </c>
       <c r="F77">
-        <v>22000</v>
+        <v>8600</v>
       </c>
       <c r="G77">
-        <v>24200</v>
+        <v>9460</v>
       </c>
       <c r="H77" t="s">
         <v>368</v>
@@ -7610,10 +7610,10 @@
         <v>333</v>
       </c>
       <c r="F78">
-        <v>22500</v>
+        <v>9000</v>
       </c>
       <c r="G78">
-        <v>24750</v>
+        <v>9900</v>
       </c>
       <c r="H78" t="s">
         <v>369</v>
@@ -7678,10 +7678,10 @@
         <v>354</v>
       </c>
       <c r="F79">
-        <v>23000</v>
+        <v>9400</v>
       </c>
       <c r="G79">
-        <v>25300</v>
+        <v>10340</v>
       </c>
       <c r="H79" t="s">
         <v>372</v>
@@ -7746,10 +7746,10 @@
         <v>349</v>
       </c>
       <c r="F80">
-        <v>23500</v>
+        <v>9800</v>
       </c>
       <c r="G80">
-        <v>25850</v>
+        <v>10780</v>
       </c>
       <c r="H80" t="s">
         <v>373</v>
@@ -7814,10 +7814,10 @@
         <v>355</v>
       </c>
       <c r="F81">
-        <v>24000</v>
+        <v>10200</v>
       </c>
       <c r="G81">
-        <v>26400</v>
+        <v>11220</v>
       </c>
       <c r="H81" t="s">
         <v>370</v>
@@ -7882,10 +7882,10 @@
         <v>356</v>
       </c>
       <c r="F82">
-        <v>24500</v>
+        <v>10600</v>
       </c>
       <c r="G82">
-        <v>26950</v>
+        <v>11660</v>
       </c>
       <c r="H82" t="s">
         <v>371</v>
@@ -7950,10 +7950,10 @@
         <v>331</v>
       </c>
       <c r="F83">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="G83">
-        <v>27500</v>
+        <v>12100</v>
       </c>
       <c r="H83" t="s">
         <v>369</v>
@@ -8018,10 +8018,10 @@
         <v>357</v>
       </c>
       <c r="F84">
-        <v>25500</v>
+        <v>11400</v>
       </c>
       <c r="G84">
-        <v>28050</v>
+        <v>12540</v>
       </c>
       <c r="H84" t="s">
         <v>369</v>
@@ -8086,10 +8086,10 @@
         <v>358</v>
       </c>
       <c r="F85">
-        <v>26000</v>
+        <v>11800</v>
       </c>
       <c r="G85">
-        <v>28600</v>
+        <v>12980</v>
       </c>
       <c r="H85" t="s">
         <v>371</v>
@@ -8154,10 +8154,10 @@
         <v>350</v>
       </c>
       <c r="F86">
-        <v>26500</v>
+        <v>12200</v>
       </c>
       <c r="G86">
-        <v>29150</v>
+        <v>13420</v>
       </c>
       <c r="H86" t="s">
         <v>373</v>
@@ -8222,10 +8222,10 @@
         <v>359</v>
       </c>
       <c r="F87">
-        <v>27000</v>
+        <v>12600</v>
       </c>
       <c r="G87">
-        <v>29700</v>
+        <v>13860</v>
       </c>
       <c r="H87" t="s">
         <v>368</v>
@@ -8290,10 +8290,10 @@
         <v>360</v>
       </c>
       <c r="F88">
-        <v>27500</v>
+        <v>13000</v>
       </c>
       <c r="G88">
-        <v>30250</v>
+        <v>14300</v>
       </c>
       <c r="H88" t="s">
         <v>371</v>
@@ -8358,10 +8358,10 @@
         <v>361</v>
       </c>
       <c r="F89">
-        <v>28000</v>
+        <v>13400</v>
       </c>
       <c r="G89">
-        <v>30800</v>
+        <v>14740</v>
       </c>
       <c r="H89" t="s">
         <v>372</v>
@@ -8426,10 +8426,10 @@
         <v>362</v>
       </c>
       <c r="F90">
-        <v>28500</v>
+        <v>13800</v>
       </c>
       <c r="G90">
-        <v>31350</v>
+        <v>15180</v>
       </c>
       <c r="H90" t="s">
         <v>369</v>
@@ -8494,10 +8494,10 @@
         <v>363</v>
       </c>
       <c r="F91">
-        <v>29000</v>
+        <v>14200</v>
       </c>
       <c r="G91">
-        <v>31900</v>
+        <v>15620</v>
       </c>
       <c r="H91" t="s">
         <v>370</v>
@@ -8562,10 +8562,10 @@
         <v>364</v>
       </c>
       <c r="F92">
-        <v>29500</v>
+        <v>14600</v>
       </c>
       <c r="G92">
-        <v>32450</v>
+        <v>16060</v>
       </c>
       <c r="H92" t="s">
         <v>373</v>
@@ -8630,10 +8630,10 @@
         <v>365</v>
       </c>
       <c r="F93">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G93">
-        <v>33000</v>
+        <v>16500</v>
       </c>
       <c r="H93" t="s">
         <v>369</v>
@@ -8698,10 +8698,10 @@
         <v>336</v>
       </c>
       <c r="F94">
-        <v>30500</v>
+        <v>15400</v>
       </c>
       <c r="G94">
-        <v>33550</v>
+        <v>16940</v>
       </c>
       <c r="H94" t="s">
         <v>371</v>
@@ -8766,10 +8766,10 @@
         <v>335</v>
       </c>
       <c r="F95">
-        <v>31000</v>
+        <v>15800</v>
       </c>
       <c r="G95">
-        <v>34100</v>
+        <v>17380</v>
       </c>
       <c r="H95" t="s">
         <v>371</v>
@@ -8834,10 +8834,10 @@
         <v>337</v>
       </c>
       <c r="F96">
-        <v>31500</v>
+        <v>16200</v>
       </c>
       <c r="G96">
-        <v>34650</v>
+        <v>17820</v>
       </c>
       <c r="H96" t="s">
         <v>369</v>
@@ -8902,10 +8902,10 @@
         <v>319</v>
       </c>
       <c r="F97">
-        <v>32000</v>
+        <v>16600</v>
       </c>
       <c r="G97">
-        <v>35200</v>
+        <v>18260</v>
       </c>
       <c r="H97" t="s">
         <v>368</v>
@@ -8970,10 +8970,10 @@
         <v>320</v>
       </c>
       <c r="F98">
-        <v>32500</v>
+        <v>17000</v>
       </c>
       <c r="G98">
-        <v>35750</v>
+        <v>18700</v>
       </c>
       <c r="H98" t="s">
         <v>373</v>
@@ -9038,10 +9038,10 @@
         <v>321</v>
       </c>
       <c r="F99">
-        <v>33000</v>
+        <v>17400</v>
       </c>
       <c r="G99">
-        <v>36300</v>
+        <v>19140</v>
       </c>
       <c r="H99" t="s">
         <v>372</v>
@@ -9106,10 +9106,10 @@
         <v>322</v>
       </c>
       <c r="F100">
-        <v>33500</v>
+        <v>17800</v>
       </c>
       <c r="G100">
-        <v>36850</v>
+        <v>19580</v>
       </c>
       <c r="H100" t="s">
         <v>371</v>
@@ -9174,10 +9174,10 @@
         <v>323</v>
       </c>
       <c r="F101">
-        <v>34000</v>
+        <v>18200</v>
       </c>
       <c r="G101">
-        <v>37400</v>
+        <v>20020</v>
       </c>
       <c r="H101" t="s">
         <v>370</v>
@@ -9242,10 +9242,10 @@
         <v>324</v>
       </c>
       <c r="F102">
-        <v>34500</v>
+        <v>18600</v>
       </c>
       <c r="G102">
-        <v>37950</v>
+        <v>20460</v>
       </c>
       <c r="H102" t="s">
         <v>369</v>
@@ -9310,10 +9310,10 @@
         <v>328</v>
       </c>
       <c r="F103">
-        <v>35000</v>
+        <v>19000</v>
       </c>
       <c r="G103">
-        <v>38500</v>
+        <v>20900</v>
       </c>
       <c r="H103" t="s">
         <v>369</v>
@@ -9378,10 +9378,10 @@
         <v>338</v>
       </c>
       <c r="F104">
-        <v>35500</v>
+        <v>19400</v>
       </c>
       <c r="G104">
-        <v>39050</v>
+        <v>21340</v>
       </c>
       <c r="H104" t="s">
         <v>373</v>
@@ -9446,10 +9446,10 @@
         <v>339</v>
       </c>
       <c r="F105">
-        <v>36000</v>
+        <v>19800</v>
       </c>
       <c r="G105">
-        <v>39600</v>
+        <v>21780</v>
       </c>
       <c r="H105" t="s">
         <v>371</v>
@@ -9514,10 +9514,10 @@
         <v>329</v>
       </c>
       <c r="F106">
-        <v>36500</v>
+        <v>20200</v>
       </c>
       <c r="G106">
-        <v>40150</v>
+        <v>22220</v>
       </c>
       <c r="H106" t="s">
         <v>371</v>
@@ -9582,10 +9582,10 @@
         <v>288</v>
       </c>
       <c r="F107">
-        <v>37000</v>
+        <v>20600</v>
       </c>
       <c r="G107">
-        <v>40700</v>
+        <v>22660</v>
       </c>
       <c r="H107" t="s">
         <v>368</v>
@@ -9650,10 +9650,10 @@
         <v>310</v>
       </c>
       <c r="F108">
-        <v>37500</v>
+        <v>21000</v>
       </c>
       <c r="G108">
-        <v>41250</v>
+        <v>23100</v>
       </c>
       <c r="H108" t="s">
         <v>369</v>
@@ -9718,10 +9718,10 @@
         <v>311</v>
       </c>
       <c r="F109">
-        <v>38000</v>
+        <v>21400</v>
       </c>
       <c r="G109">
-        <v>41800</v>
+        <v>23540</v>
       </c>
       <c r="H109" t="s">
         <v>372</v>
@@ -9786,10 +9786,10 @@
         <v>307</v>
       </c>
       <c r="F110">
-        <v>38500</v>
+        <v>21800</v>
       </c>
       <c r="G110">
-        <v>42350</v>
+        <v>23980</v>
       </c>
       <c r="H110" t="s">
         <v>373</v>
@@ -9854,10 +9854,10 @@
         <v>312</v>
       </c>
       <c r="F111">
-        <v>39000</v>
+        <v>22200</v>
       </c>
       <c r="G111">
-        <v>42900</v>
+        <v>24420</v>
       </c>
       <c r="H111" t="s">
         <v>370</v>
@@ -9922,10 +9922,10 @@
         <v>285</v>
       </c>
       <c r="F112">
-        <v>39500</v>
+        <v>22600</v>
       </c>
       <c r="G112">
-        <v>43450</v>
+        <v>24860</v>
       </c>
       <c r="H112" t="s">
         <v>371</v>
@@ -9990,10 +9990,10 @@
         <v>340</v>
       </c>
       <c r="F113">
-        <v>40000</v>
+        <v>23000</v>
       </c>
       <c r="G113">
-        <v>44000</v>
+        <v>25300</v>
       </c>
       <c r="H113" t="s">
         <v>369</v>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meu Computador\Desktop\Clean Trabalho\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0689D9C8-A675-4D7A-9641-E77202A2D472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA0BE457-E36A-4D33-9EB8-EC119843CD00}"/>
+    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
   <si>
     <t>100002</t>
   </si>
@@ -172,12 +171,42 @@
   </si>
   <si>
     <t>XCD</t>
+  </si>
+  <si>
+    <t>400001</t>
+  </si>
+  <si>
+    <t>448001</t>
+  </si>
+  <si>
+    <t>2025-08-10</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
+  </si>
+  <si>
+    <t>Medidor de Vazão Fixo</t>
+  </si>
+  <si>
+    <t>ADP</t>
+  </si>
+  <si>
+    <t>PROD400001</t>
+  </si>
+  <si>
+    <t>Produto de Teste - Processo 400001</t>
+  </si>
+  <si>
+    <t>MATEUS BORRO MACHADO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -230,11 +259,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -548,8 +578,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D438093-7464-46A3-87DA-40F4B4EBC2C2}">
-  <dimension ref="A1:X3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:X4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -560,9 +590,9 @@
     <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -666,10 +696,10 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <v>12000</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>13200</v>
+        <v>50</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -730,14 +760,14 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
-        <v>4</v>
+      <c r="E3" s="2">
+        <v>45885</v>
       </c>
       <c r="F3">
-        <v>12000</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>13200</v>
+        <v>20</v>
       </c>
       <c r="H3" t="s">
         <v>5</v>
@@ -782,10 +812,82 @@
         <v>18</v>
       </c>
       <c r="W3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45870</v>
+      </c>
+      <c r="F4">
+        <v>70</v>
+      </c>
+      <c r="G4">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" t="s">
+        <v>14</v>
+      </c>
+      <c r="S4" t="s">
+        <v>15</v>
+      </c>
+      <c r="T4" t="s">
+        <v>53</v>
+      </c>
+      <c r="U4" t="s">
+        <v>54</v>
+      </c>
+      <c r="V4" t="s">
+        <v>18</v>
+      </c>
+      <c r="W4" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meu Computador\Desktop\Clean Trabalho\PROJETO_COMISSOES_V2\dados_entrada\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F12953A-53AB-468F-A26B-BB5C1D6C6FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -19,21 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
   <si>
     <t>100002</t>
   </si>
@@ -201,12 +193,15 @@
   </si>
   <si>
     <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>PENDENTE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -578,8 +573,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:X5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -886,6 +881,74 @@
         <v>19</v>
       </c>
     </row>
+    <row r="5" spans="1:24" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>100001</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>48002</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" t="s">
+        <v>7</v>
+      </c>
+      <c r="L5" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S5" t="s">
+        <v>15</v>
+      </c>
+      <c r="T5" t="s">
+        <v>16</v>
+      </c>
+      <c r="U5" t="s">
+        <v>17</v>
+      </c>
+      <c r="V5" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F12953A-53AB-468F-A26B-BB5C1D6C6FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453A0084-DE02-4862-8673-FDABE2638B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -881,7 +890,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>100001</v>
       </c>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453A0084-DE02-4862-8673-FDABE2638B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537C751E-02C5-451F-85C6-5CADB4663706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
   <si>
     <t>100002</t>
   </si>
@@ -900,9 +900,6 @@
       <c r="C5">
         <v>48002</v>
       </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
       <c r="E5" t="s">
         <v>4</v>
       </c>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537C751E-02C5-451F-85C6-5CADB4663706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6066346A-9586-4E11-B201-D6B0961F4190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="56">
   <si>
     <t>100002</t>
   </si>
@@ -202,9 +202,6 @@
   </si>
   <si>
     <t>MATEUS BORRO MACHADO</t>
-  </si>
-  <si>
-    <t>PENDENTE</t>
   </si>
 </sst>
 </file>
@@ -895,10 +892,13 @@
         <v>100001</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>48002</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6066346A-9586-4E11-B201-D6B0961F4190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E746E5-881D-48BA-8928-1DC90CC2F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,65 +34,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="56">
-  <si>
-    <t>100002</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="40">
   <si>
     <t>FATURADO</t>
   </si>
   <si>
-    <t>048001</t>
-  </si>
-  <si>
-    <t>2025-08-25</t>
-  </si>
-  <si>
-    <t>2025-07-16</t>
-  </si>
-  <si>
-    <t>ANDREY.ANDRADE</t>
-  </si>
-  <si>
-    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
-  </si>
-  <si>
-    <t>SSO</t>
-  </si>
-  <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Industrial</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>CLIENTE TESTE LTDA</t>
-  </si>
-  <si>
-    <t>São Paulo</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>PROD100002</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 100002</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>PVEN - Produto Venda</t>
   </si>
   <si>
@@ -168,21 +117,6 @@
     <t>Fabricante</t>
   </si>
   <si>
-    <t>Detector Fixo</t>
-  </si>
-  <si>
-    <t>XCD</t>
-  </si>
-  <si>
-    <t>400001</t>
-  </si>
-  <si>
-    <t>448001</t>
-  </si>
-  <si>
-    <t>2025-08-10</t>
-  </si>
-  <si>
     <t>SAMANTA</t>
   </si>
   <si>
@@ -192,16 +126,34 @@
     <t>Medidor de Vazão Fixo</t>
   </si>
   <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>PROD400001</t>
-  </si>
-  <si>
-    <t>Produto de Teste - Processo 400001</t>
-  </si>
-  <si>
     <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
+    <t>Sonda Serie EXO</t>
+  </si>
+  <si>
+    <t>EXO</t>
+  </si>
+  <si>
+    <t>YSI</t>
+  </si>
+  <si>
+    <t>TESTE2</t>
+  </si>
+  <si>
+    <t>TESTE</t>
+  </si>
+  <si>
+    <t>IQ Standard</t>
+  </si>
+  <si>
+    <t>TESTE3</t>
+  </si>
+  <si>
+    <t>TESTE4</t>
+  </si>
+  <si>
+    <t>TESTE5</t>
   </si>
 </sst>
 </file>
@@ -580,10 +532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -594,7 +546,7 @@
     <col min="9" max="10" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -606,163 +558,148 @@
     <col min="24" max="24" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2">
+        <v>999222</v>
+      </c>
+      <c r="D2" s="2">
+        <v>45170</v>
+      </c>
+      <c r="E2" s="2">
+        <v>45170</v>
+      </c>
+      <c r="F2">
+        <v>30</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="P2">
+        <v>1111</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>35</v>
+      </c>
+      <c r="W2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>50</v>
-      </c>
-      <c r="G2">
-        <v>50</v>
-      </c>
-      <c r="H2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" t="s">
-        <v>10</v>
-      </c>
-      <c r="O2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s">
-        <v>18</v>
-      </c>
-      <c r="W2" t="s">
-        <v>19</v>
+      <c r="X2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
+      <c r="C3">
+        <v>999222</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45170</v>
       </c>
       <c r="E3" s="2">
-        <v>45885</v>
+        <v>45170</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -771,188 +708,299 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1111</v>
       </c>
       <c r="Q3" t="s">
-        <v>13</v>
-      </c>
-      <c r="R3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S3" t="s">
-        <v>15</v>
-      </c>
-      <c r="T3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U3" t="s">
-        <v>17</v>
-      </c>
-      <c r="V3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="W3" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="X3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>999111</v>
+      </c>
+      <c r="D4" s="2">
+        <v>45170</v>
+      </c>
+      <c r="E4" s="2">
+        <v>45170</v>
+      </c>
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="2">
-        <v>45870</v>
-      </c>
-      <c r="F4">
-        <v>70</v>
-      </c>
-      <c r="G4">
-        <v>70</v>
-      </c>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P4" t="s">
-        <v>12</v>
+      <c r="P4">
+        <v>1112</v>
       </c>
       <c r="Q4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S4" t="s">
-        <v>15</v>
-      </c>
-      <c r="T4" t="s">
-        <v>53</v>
-      </c>
-      <c r="U4" t="s">
-        <v>54</v>
-      </c>
-      <c r="V4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="W4" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="X4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>100001</v>
+      <c r="A5" t="s">
+        <v>37</v>
       </c>
       <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>999000</v>
+      </c>
+      <c r="D5" s="2">
+        <v>45170</v>
+      </c>
+      <c r="E5" s="2">
+        <v>45170</v>
+      </c>
+      <c r="F5">
+        <v>30</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>48002</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>50</v>
-      </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
-      <c r="H5" t="s">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" t="s">
-        <v>12</v>
+      <c r="P5">
+        <v>1111</v>
       </c>
       <c r="Q5" t="s">
-        <v>13</v>
-      </c>
-      <c r="R5" t="s">
-        <v>14</v>
-      </c>
-      <c r="S5" t="s">
-        <v>15</v>
-      </c>
-      <c r="T5" t="s">
-        <v>16</v>
-      </c>
-      <c r="U5" t="s">
-        <v>17</v>
-      </c>
-      <c r="V5" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="W5" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="X5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>999001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>45931</v>
+      </c>
+      <c r="E6" s="2">
+        <v>45901</v>
+      </c>
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1111</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>35</v>
+      </c>
+      <c r="W6" t="s">
+        <v>2</v>
+      </c>
+      <c r="X6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>999001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45901</v>
+      </c>
+      <c r="F7">
+        <v>20</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1111</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" t="s">
+        <v>2</v>
+      </c>
+      <c r="X7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>999002</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45941</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45931</v>
+      </c>
+      <c r="F8">
+        <v>30</v>
+      </c>
+      <c r="G8">
+        <v>30</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="M8" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1112</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" t="s">
+        <v>2</v>
+      </c>
+      <c r="X8" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E746E5-881D-48BA-8928-1DC90CC2F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE7A609-74A8-4254-9F1C-01897E80447D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -643,10 +643,10 @@
         <v>999222</v>
       </c>
       <c r="D2" s="2">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="E2" s="2">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="F2">
         <v>30</v>
@@ -696,10 +696,10 @@
         <v>999222</v>
       </c>
       <c r="D3" s="2">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="E3" s="2">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -749,10 +749,10 @@
         <v>999111</v>
       </c>
       <c r="D4" s="2">
-        <v>45170</v>
+        <v>45201</v>
       </c>
       <c r="E4" s="2">
-        <v>45170</v>
+        <v>45201</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -802,10 +802,10 @@
         <v>999000</v>
       </c>
       <c r="D5" s="2">
-        <v>45170</v>
+        <v>45202</v>
       </c>
       <c r="E5" s="2">
-        <v>45170</v>
+        <v>45202</v>
       </c>
       <c r="F5">
         <v>30</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="P5">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="Q5" t="s">
         <v>37</v>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE7A609-74A8-4254-9F1C-01897E80447D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F36795E-1F6A-45C1-A37F-31629D15EB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
   <si>
     <t>FATURADO</t>
   </si>
@@ -154,6 +155,9 @@
   </si>
   <si>
     <t>TESTE5</t>
+  </si>
+  <si>
+    <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
   </si>
 </sst>
 </file>
@@ -872,6 +876,9 @@
       <c r="I6" t="s">
         <v>30</v>
       </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
       <c r="K6" t="s">
         <v>28</v>
       </c>
@@ -924,6 +931,9 @@
       </c>
       <c r="I7" t="s">
         <v>30</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>

--- a/dados_entrada/Analise_Comercial_Completa.xlsx
+++ b/dados_entrada/Analise_Comercial_Completa.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F36795E-1F6A-45C1-A37F-31629D15EB78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F618EE65-0B9A-4DC7-8978-58D29B6017D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="43">
   <si>
     <t>FATURADO</t>
   </si>
@@ -158,13 +157,19 @@
   </si>
   <si>
     <t>ANDRÉ LUIS GONCALVES CAMARGO</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>BBB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +179,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -216,12 +229,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -536,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -682,6 +696,9 @@
       <c r="Q2" t="s">
         <v>35</v>
       </c>
+      <c r="T2" t="s">
+        <v>41</v>
+      </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
@@ -735,6 +752,9 @@
       <c r="Q3" t="s">
         <v>35</v>
       </c>
+      <c r="T3" t="s">
+        <v>42</v>
+      </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
@@ -788,6 +808,9 @@
       <c r="Q4" t="s">
         <v>34</v>
       </c>
+      <c r="T4" t="s">
+        <v>41</v>
+      </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
@@ -841,6 +864,9 @@
       <c r="Q5" t="s">
         <v>37</v>
       </c>
+      <c r="T5" t="s">
+        <v>41</v>
+      </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
@@ -897,6 +923,9 @@
       <c r="Q6" t="s">
         <v>35</v>
       </c>
+      <c r="T6" t="s">
+        <v>41</v>
+      </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
@@ -953,6 +982,9 @@
       <c r="Q7" t="s">
         <v>35</v>
       </c>
+      <c r="T7" t="s">
+        <v>42</v>
+      </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
@@ -1006,12 +1038,18 @@
       <c r="Q8" t="s">
         <v>34</v>
       </c>
+      <c r="T8" t="s">
+        <v>41</v>
+      </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
         <v>33</v>
       </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="S11" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
